--- a/data/trans_dic/IMC_inf_MED_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,45; 70,97</t>
+          <t>43,41; 71,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,5; 64,09</t>
+          <t>33,64; 60,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 53,49</t>
+          <t>11,0; 51,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,88; 68,64</t>
+          <t>38,7; 67,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,33; 68,96</t>
+          <t>38,07; 70,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,08; 74,72</t>
+          <t>26,3; 74,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,08; 66,35</t>
+          <t>45,54; 65,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,0; 60,6</t>
+          <t>40,07; 61,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,28; 54,81</t>
+          <t>23,28; 55,3</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,21; 56,98</t>
+          <t>44,87; 57,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,16; 44,85</t>
+          <t>32,21; 44,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,89; 54,09</t>
+          <t>32,28; 54,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56,67; 68,27</t>
+          <t>57,24; 68,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,68; 55,14</t>
+          <t>43,1; 55,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,44; 60,4</t>
+          <t>41,42; 59,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,0; 61,48</t>
+          <t>53,01; 61,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,75; 49,1</t>
+          <t>40,88; 49,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,25; 54,73</t>
+          <t>40,3; 54,79</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,02; 60,8</t>
+          <t>46,19; 60,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,25; 44,18</t>
+          <t>31,6; 44,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,91; 51,83</t>
+          <t>30,8; 51,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,02; 59,97</t>
+          <t>46,76; 60,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,11; 58,17</t>
+          <t>44,8; 58,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,01; 54,9</t>
+          <t>35,29; 53,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,71; 58,85</t>
+          <t>48,57; 58,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,54; 48,93</t>
+          <t>39,61; 48,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,48; 50,07</t>
+          <t>36,36; 50,35</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,07; 33,45</t>
+          <t>21,12; 33,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,98; 30,27</t>
+          <t>18,91; 31,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 22,25</t>
+          <t>6,19; 22,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,49; 48,83</t>
+          <t>35,78; 48,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,6; 39,04</t>
+          <t>25,81; 39,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,84; 42,0</t>
+          <t>23,19; 42,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,79; 38,67</t>
+          <t>30,24; 39,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,3; 32,73</t>
+          <t>24,17; 32,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,77; 29,41</t>
+          <t>15,95; 30,3</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,41; 48,75</t>
+          <t>41,02; 48,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,35; 38,04</t>
+          <t>31,4; 38,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,15; 34,05</t>
+          <t>19,62; 34,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,18; 57,6</t>
+          <t>50,0; 57,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,91; 48,97</t>
+          <t>41,6; 48,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,95; 46,67</t>
+          <t>36,08; 46,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,0; 51,97</t>
+          <t>46,8; 51,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,67; 42,87</t>
+          <t>37,96; 42,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,29; 39,01</t>
+          <t>29,76; 39,25</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>18051</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13169</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3811</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14224</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13879</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32275</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>27047</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>8813</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>13438; 21992</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9401; 16885</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1454; 6792</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10189; 17844</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9766; 18141</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2581; 7333</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>26086; 37513</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>21477; 32770</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5362; 12736</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>96295</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>64246</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24496</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>131195</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98871</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>41765</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>227490</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>163117</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>66261</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>84513; 107419</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>53036; 73140</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>18452; 31253</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>119414; 141856</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>85863; 110210</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>34159; 49130</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>210425; 243130</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>148725; 179779</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>56263; 76505</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>70781</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57635</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28323</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>71608</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>78130</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>42261</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>142389</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>135765</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>60942; 79894</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>48592; 68003</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21462; 35989</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>62623; 81316</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>68658; 89215</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>33689; 51274</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>129124; 154804</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>121622; 150177</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>60044; 83158</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>40387</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>34437</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16845</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>63889</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>46920</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>40832</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>104276</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>81357</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>57677</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>31547; 50720</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26634; 44539</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7730; 27726</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>55233; 74185</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>37714; 57121</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>29814; 54252</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>91849; 119266</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>69372; 94204</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>40414; 76770</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>225514</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>169486</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>73475</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>280916</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>237801</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>129860</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>506430</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>407287</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>203335</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>205390; 243812</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>152963; 186468</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>51965; 90986</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>261595; 299338</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>218058; 256355</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>114136; 147287</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>479173; 530908</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>383953; 434542</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>172988; 228107</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IMC_inf_MED_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición) (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,41; 71,04</t>
+          <t>43,62; 70,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,64; 60,42</t>
+          <t>32,71; 62,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,0; 51,37</t>
+          <t>12,53; 54,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,7; 67,78</t>
+          <t>38,5; 69,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,07; 70,72</t>
+          <t>38,97; 69,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,3; 74,75</t>
+          <t>27,57; 75,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,54; 65,48</t>
+          <t>46,15; 66,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,07; 61,14</t>
+          <t>40,53; 61,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,28; 55,3</t>
+          <t>23,09; 54,62</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>44,87; 57,03</t>
+          <t>44,73; 57,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,21; 44,43</t>
+          <t>33,08; 44,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,28; 54,68</t>
+          <t>32,36; 54,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57,24; 68,0</t>
+          <t>56,9; 68,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,1; 55,33</t>
+          <t>44,42; 55,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,42; 59,57</t>
+          <t>40,81; 59,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,01; 61,24</t>
+          <t>53,38; 61,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,88; 49,41</t>
+          <t>40,64; 49,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,3; 54,79</t>
+          <t>40,77; 54,2</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,19; 60,55</t>
+          <t>46,86; 61,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,6; 44,23</t>
+          <t>31,47; 44,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,8; 51,64</t>
+          <t>30,39; 52,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,76; 60,72</t>
+          <t>46,15; 60,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,8; 58,21</t>
+          <t>44,0; 57,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,29; 53,71</t>
+          <t>34,83; 53,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,57; 58,22</t>
+          <t>48,9; 58,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,61; 48,92</t>
+          <t>39,48; 48,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,36; 50,35</t>
+          <t>36,05; 50,51</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,12; 33,95</t>
+          <t>20,32; 33,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,91; 31,62</t>
+          <t>18,91; 31,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 22,22</t>
+          <t>6,31; 21,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,78; 48,06</t>
+          <t>35,19; 47,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,81; 39,09</t>
+          <t>25,65; 38,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,19; 42,19</t>
+          <t>24,11; 41,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,24; 39,26</t>
+          <t>29,68; 38,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,17; 32,83</t>
+          <t>24,07; 32,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,95; 30,3</t>
+          <t>15,87; 29,75</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,02; 48,7</t>
+          <t>41,87; 48,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,4; 38,27</t>
+          <t>31,07; 38,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,62; 34,35</t>
+          <t>20,21; 33,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,0; 57,21</t>
+          <t>50,03; 57,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,6; 48,9</t>
+          <t>41,9; 49,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,08; 46,56</t>
+          <t>35,56; 46,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,8; 51,85</t>
+          <t>46,91; 52,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,96; 42,96</t>
+          <t>37,74; 42,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,76; 39,25</t>
+          <t>29,45; 39,19</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición) (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13438; 21992</t>
+          <t>13502; 21973</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9401; 16885</t>
+          <t>9143; 17336</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1454; 6792</t>
+          <t>1657; 7179</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10189; 17844</t>
+          <t>10138; 18347</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9766; 18141</t>
+          <t>9995; 17922</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2581; 7333</t>
+          <t>2705; 7395</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26086; 37513</t>
+          <t>26438; 38103</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21477; 32770</t>
+          <t>21724; 32801</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5362; 12736</t>
+          <t>5317; 12579</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84513; 107419</t>
+          <t>84257; 107418</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53036; 73140</t>
+          <t>54456; 73738</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18452; 31253</t>
+          <t>18493; 31031</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>119414; 141856</t>
+          <t>118706; 142956</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85863; 110210</t>
+          <t>88478; 110916</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34159; 49130</t>
+          <t>33656; 49248</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>210425; 243130</t>
+          <t>211931; 243766</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>148725; 179779</t>
+          <t>147852; 178568</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56263; 76505</t>
+          <t>56930; 75673</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>60942; 79894</t>
+          <t>61831; 80545</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48592; 68003</t>
+          <t>48384; 68929</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21462; 35989</t>
+          <t>21177; 36677</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62623; 81316</t>
+          <t>61814; 81036</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68658; 89215</t>
+          <t>67428; 88349</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33689; 51274</t>
+          <t>33254; 50827</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>129124; 154804</t>
+          <t>130013; 155266</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>121622; 150177</t>
+          <t>121217; 149958</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>60044; 83158</t>
+          <t>59542; 83419</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31547; 50720</t>
+          <t>30361; 49397</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26634; 44539</t>
+          <t>26640; 44295</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7730; 27726</t>
+          <t>7873; 26757</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55233; 74185</t>
+          <t>54315; 73945</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37714; 57121</t>
+          <t>37474; 56779</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29814; 54252</t>
+          <t>30997; 53602</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>91849; 119266</t>
+          <t>90162; 118328</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69372; 94204</t>
+          <t>69073; 93974</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40414; 76770</t>
+          <t>40215; 75391</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>205390; 243812</t>
+          <t>209635; 244360</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>152963; 186468</t>
+          <t>151353; 186167</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51965; 90986</t>
+          <t>53537; 89794</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>261595; 299338</t>
+          <t>261767; 299156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>218058; 256355</t>
+          <t>219625; 259167</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>114136; 147287</t>
+          <t>112479; 147517</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>479173; 530908</t>
+          <t>480298; 536733</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>383953; 434542</t>
+          <t>381664; 432825</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>172988; 228107</t>
+          <t>171148; 227743</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_MED_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>54,03%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>54,11%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>54,67%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>58,31%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>47,12%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28,82%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>54,03%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>54,11%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,62; 70,98</t>
+          <t>37,88; 68,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,71; 62,03</t>
+          <t>38,33; 68,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,53; 54,31</t>
+          <t>30,78; 77,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,5; 69,69</t>
+          <t>43,45; 70,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,97; 69,87</t>
+          <t>32,5; 64,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,57; 75,37</t>
+          <t>12,19; 54,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,15; 66,51</t>
+          <t>45,08; 66,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,53; 61,2</t>
+          <t>39,0; 60,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,09; 54,62</t>
+          <t>24,34; 56,02</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>62,89%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49,64%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>49,76%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>51,12%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>39,02%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>42,86%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>62,89%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>49,64%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>44,73; 57,03</t>
+          <t>56,67; 68,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,08; 44,79</t>
+          <t>43,68; 55,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,36; 54,29</t>
+          <t>40,81; 60,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56,9; 68,52</t>
+          <t>45,21; 56,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,42; 55,68</t>
+          <t>33,16; 44,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,81; 59,72</t>
+          <t>30,71; 51,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,38; 61,4</t>
+          <t>53,0; 61,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,64; 49,08</t>
+          <t>40,75; 49,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,77; 54,2</t>
+          <t>38,88; 52,72</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>53,47%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50,98%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45,12%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>53,64%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>37,48%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40,64%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>53,47%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>50,98%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,17%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,86; 61,04</t>
+          <t>46,02; 59,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,47; 44,83</t>
+          <t>44,11; 58,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,39; 52,63</t>
+          <t>35,88; 55,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,15; 60,51</t>
+          <t>46,02; 60,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,0; 57,65</t>
+          <t>31,25; 44,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,83; 53,24</t>
+          <t>28,61; 47,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,9; 58,4</t>
+          <t>48,71; 58,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,48; 48,84</t>
+          <t>39,54; 48,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,05; 50,51</t>
+          <t>35,13; 49,27</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41,39%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32,11%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32,34%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>27,03%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>24,45%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41,39%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>32,11%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,32; 33,06</t>
+          <t>35,49; 48,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,91; 31,45</t>
+          <t>25,6; 39,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 21,44</t>
+          <t>24,34; 41,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,19; 47,91</t>
+          <t>21,07; 33,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,65; 38,86</t>
+          <t>18,98; 30,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,11; 41,69</t>
+          <t>9,44; 21,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,68; 38,96</t>
+          <t>29,79; 38,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,07; 32,75</t>
+          <t>24,3; 32,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,87; 29,75</t>
+          <t>19,03; 30,23</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>53,69%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>45,36%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>45,04%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>34,79%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>53,69%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>45,36%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,87; 48,81</t>
+          <t>50,18; 57,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,07; 38,21</t>
+          <t>41,91; 48,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,21; 33,9</t>
+          <t>35,96; 46,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,03; 57,17</t>
+          <t>41,41; 48,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,9; 49,44</t>
+          <t>31,35; 38,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,56; 46,63</t>
+          <t>23,22; 33,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,91; 52,42</t>
+          <t>47,0; 51,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,74; 42,79</t>
+          <t>37,67; 42,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,45; 39,19</t>
+          <t>31,5; 39,14</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14224</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13879</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>18051</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>13169</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3811</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14224</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13879</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>8077</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13502; 21973</t>
+          <t>9973; 18071</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9143; 17336</t>
+          <t>9833; 17690</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1657; 7179</t>
+          <t>2424; 6098</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10138; 18347</t>
+          <t>13449; 21971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9995; 17922</t>
+          <t>9084; 17912</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2705; 7395</t>
+          <t>1537; 6870</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26438; 38103</t>
+          <t>25827; 38011</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21724; 32801</t>
+          <t>20901; 32478</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5317; 12579</t>
+          <t>4986; 11476</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>131195</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>98871</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34801</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>96295</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>64246</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>24496</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>131195</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98871</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41765</t>
+          <t>20654</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>66261</t>
+          <t>55455</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84257; 107418</t>
+          <t>118236; 142422</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54456; 73738</t>
+          <t>87000; 109837</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18493; 31031</t>
+          <t>28546; 42049</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>118706; 142956</t>
+          <t>85169; 107326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88478; 110916</t>
+          <t>54593; 73844</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33656; 49248</t>
+          <t>15707; 26580</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>211931; 243766</t>
+          <t>210410; 244054</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>147852; 178568</t>
+          <t>148256; 178642</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56930; 75673</t>
+          <t>47078; 63832</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>71608</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>78130</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>41987</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>70781</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>57635</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28323</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>71608</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>78130</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42261</t>
+          <t>26386</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70584</t>
+          <t>68373</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>61831; 80545</t>
+          <t>61641; 80312</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48384; 68929</t>
+          <t>67602; 89148</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21177; 36677</t>
+          <t>33389; 51833</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61814; 81036</t>
+          <t>60720; 80224</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67428; 88349</t>
+          <t>48056; 67928</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33254; 50827</t>
+          <t>19761; 32900</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>130013; 155266</t>
+          <t>129514; 156454</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>121217; 149958</t>
+          <t>121404; 150209</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>59542; 83419</t>
+          <t>56957; 79889</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63889</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>46920</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>40245</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>40387</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>34437</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16845</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>63889</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>46920</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40832</t>
+          <t>15268</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57677</t>
+          <t>55513</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30361; 49397</t>
+          <t>54787; 75368</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26640; 44295</t>
+          <t>37403; 57043</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7873; 26757</t>
+          <t>30288; 51863</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54315; 73945</t>
+          <t>31483; 49982</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37474; 56779</t>
+          <t>26738; 42635</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30997; 53602</t>
+          <t>9760; 22623</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90162; 118328</t>
+          <t>90485; 117460</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69073; 93974</t>
+          <t>69738; 93924</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40215; 75391</t>
+          <t>43361; 68864</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>322</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>252</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>104</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>280916</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>237801</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>121338</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>225514</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>169486</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>73475</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>280916</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>237801</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>129860</t>
+          <t>66080</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>203335</t>
+          <t>187419</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>209635; 244360</t>
+          <t>262560; 301398</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>151353; 186167</t>
+          <t>219700; 256707</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53537; 89794</t>
+          <t>106201; 137074</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>261767; 299156</t>
+          <t>207320; 244101</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>219625; 259167</t>
+          <t>152738; 185334</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>112479; 147517</t>
+          <t>54849; 78050</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>480298; 536733</t>
+          <t>481200; 532083</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>381664; 432825</t>
+          <t>380987; 433598</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>171148; 227743</t>
+          <t>167434; 208024</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_MED_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Edad-trans_dic.xlsx
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 71,23%)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.5402623576903324</v>
+        <v>0.4367053078668813</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.5410854004757066</v>
+        <v>0.507818368460809</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0.5466521385885758</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.5831012649919657</v>
+        <v>0.5675937061756184</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.4711814736004449</v>
+        <v>0.477437054667924</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0.2991508700710264</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.5634127523273292</v>
+        <v>0.5078455997807187</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.5046356082925827</v>
+        <v>0.4923665970974344</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>0.3943065256584083</v>
@@ -667,28 +667,28 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.3787841147387206</v>
+        <v>0.2916149029298357</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.3833241100611158</v>
+        <v>0.3725129234635024</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0.307818895791851</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.4344513909415435</v>
+        <v>0.4476510761806652</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.3250304471159828</v>
+        <v>0.3538438618181897</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0.121913461088141</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.4508428306117745</v>
+        <v>0.4180353936721968</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.3899608352139688</v>
+        <v>0.3882870128188092</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0.2433894954922967</v>
@@ -702,28 +702,28 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.6863751964660718</v>
+        <v>0.5634357602668972</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.6896356075896365</v>
+        <v>0.6605413912001842</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0.7742291758822704</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.7097372292513752</v>
+        <v>0.6902969068528363</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.6409083490116356</v>
+        <v>0.6162453788877985</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0.544811403486654</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.6635486798627775</v>
+        <v>0.6039411093178538</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.6059603352661133</v>
+        <v>0.5944850612336808</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0.5602169815887306</v>
@@ -741,31 +741,31 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.6288601103688418</v>
+        <v>0.5968208640121002</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.4963501306233004</v>
+        <v>0.4786287378970188</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.4975666117257556</v>
+        <v>0.4907691539336634</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.5112107764370339</v>
+        <v>0.5092527518596922</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.3902326895772182</v>
+        <v>0.3886522192376666</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.4038599361124355</v>
+        <v>0.417348406910227</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.5730371096170376</v>
+        <v>0.5557217943232319</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.4483318971362662</v>
+        <v>0.438688399034185</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.4579881086804841</v>
+        <v>0.4594059959909861</v>
       </c>
     </row>
     <row r="8">
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.5667410681351982</v>
+        <v>0.5426853904684834</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.4367536402980728</v>
+        <v>0.428552587159933</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.4081452781520847</v>
+        <v>0.4030774872697264</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.4521443141743338</v>
+        <v>0.4537065731130308</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.3316004463793189</v>
+        <v>0.3352361582252018</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.3071271958719704</v>
+        <v>0.3265675048788706</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.530014118219755</v>
+        <v>0.5199249534003878</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.4074859156408041</v>
+        <v>0.4048235395980103</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.3888055639513798</v>
+        <v>0.3907040039943658</v>
       </c>
     </row>
     <row r="9">
@@ -811,31 +811,31 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.6826721409526995</v>
+        <v>0.6475220780930443</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.5513968575642868</v>
+        <v>0.5341569479902228</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.6011987306704191</v>
+        <v>0.5876261818821004</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.5697746108050366</v>
+        <v>0.5612822954422387</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.448535810370325</v>
+        <v>0.4405528250287128</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.5197318640812608</v>
+        <v>0.5157426440261176</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.6147598761276821</v>
+        <v>0.594040560811091</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.4910031318681566</v>
+        <v>0.481371563348809</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.5271722607045563</v>
+        <v>0.5326361099706399</v>
       </c>
     </row>
     <row r="10">
@@ -850,31 +850,31 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.534667578987721</v>
+        <v>0.5441022278523743</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.5097998626875803</v>
+        <v>0.50406793525588</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.4512007743410978</v>
+        <v>0.4492666121698651</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.5364489709032121</v>
+        <v>0.510006448213856</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.3748462438304267</v>
+        <v>0.364178038392152</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.3819484754500291</v>
+        <v>0.3929672875269292</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.5355516198881444</v>
+        <v>0.527138989462073</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.4422133325284838</v>
+        <v>0.4335334917831102</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.4216946828528128</v>
+        <v>0.4248943244783879</v>
       </c>
     </row>
     <row r="11">
@@ -885,31 +885,31 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.4602493471532809</v>
+        <v>0.4821908638852258</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.4411032422835711</v>
+        <v>0.4421438457337736</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.3588018948315005</v>
+        <v>0.3590238620686925</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.4601927905471597</v>
+        <v>0.4448999241713019</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.3125472354301158</v>
+        <v>0.3092299173279012</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.2860539199486997</v>
+        <v>0.2995577605800281</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.4871237031648518</v>
+        <v>0.4825485366057491</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.3954355192483691</v>
+        <v>0.3908987811766894</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.3512847681416058</v>
+        <v>0.3537136932658245</v>
       </c>
     </row>
     <row r="12">
@@ -920,31 +920,31 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.5996600757999111</v>
+        <v>0.6064626716361204</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.5816886149112509</v>
+        <v>0.5630746180885317</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.5569988757886388</v>
+        <v>0.5440154245409522</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.6080167820673635</v>
+        <v>0.575966809400885</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.4417881567747411</v>
+        <v>0.4239273116509774</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.4762404484601391</v>
+        <v>0.4911068348652348</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.5884521501003348</v>
+        <v>0.5747003763205749</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.4892582571827442</v>
+        <v>0.4744557503221206</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.4927213211580433</v>
+        <v>0.493513373289573</v>
       </c>
     </row>
     <row r="13">
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.4139178008601011</v>
+        <v>0.4006537530135227</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.3211120151703006</v>
+        <v>0.3386983661031804</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.3234074493580646</v>
+        <v>0.3281437830052117</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.2703226782299903</v>
+        <v>0.2817457552615616</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.2444767858635145</v>
+        <v>0.2287944436990382</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.1476843742340614</v>
+        <v>0.1441066044189455</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.3432900973602649</v>
+        <v>0.3420550545213199</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.2834960334322737</v>
+        <v>0.2849806945216043</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.2436654635904065</v>
+        <v>0.2454903606242617</v>
       </c>
     </row>
     <row r="14">
@@ -994,31 +994,31 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.3549453618007793</v>
+        <v>0.3420401042836548</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.2559771706121987</v>
+        <v>0.2781004603864018</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.243396173226718</v>
+        <v>0.2489695411634774</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.2107227455289064</v>
+        <v>0.2291313734646966</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.189820460673078</v>
+        <v>0.1740608062636012</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.09439964962801552</v>
+        <v>0.09450059556166344</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.2978888176879267</v>
+        <v>0.3013579347050922</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.2430098094074735</v>
+        <v>0.2412449342065583</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.1903245010039695</v>
+        <v>0.1946559560443031</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.4882833008438157</v>
+        <v>0.4594888676858229</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.390391675973446</v>
+        <v>0.4044734198855709</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.4167749080016044</v>
+        <v>0.4205504678136447</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.3345426449121877</v>
+        <v>0.3409178157791968</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.3026747272513188</v>
+        <v>0.2858754019113036</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.2188176780081332</v>
+        <v>0.2165608588327953</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.386694555624209</v>
+        <v>0.3871340243776084</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.3272868806366763</v>
+        <v>0.3297323258102711</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.3022673912562037</v>
+        <v>0.307876255866775</v>
       </c>
     </row>
     <row r="16">
@@ -1068,31 +1068,31 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.5368847747166713</v>
+        <v>0.5194073618784171</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.4536268504821084</v>
+        <v>0.4498187677890572</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.410877839109871</v>
+        <v>0.4106948042901157</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.4504246060940044</v>
+        <v>0.4480993812094337</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.3478785913841982</v>
+        <v>0.3410060676206463</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.2797420285860966</v>
+        <v>0.2874848544914089</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.4946073589230291</v>
+        <v>0.4846192482017541</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.4026881249815326</v>
+        <v>0.3978428558400455</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.3525997894573501</v>
+        <v>0.3558486175747382</v>
       </c>
     </row>
     <row r="17">
@@ -1103,31 +1103,31 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.5018018298204001</v>
+        <v>0.4849276368679208</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.4190984251942523</v>
+        <v>0.4154058591283558</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.3596202801771443</v>
+        <v>0.360849822429133</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.4140860597102639</v>
+        <v>0.4136218620576</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.3135019948392222</v>
+        <v>0.3095667519334427</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.2321959483809797</v>
+        <v>0.2424683607083414</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.4699657488694993</v>
+        <v>0.4618263964367272</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.3766850554496688</v>
+        <v>0.3739540851910583</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.3150023636177863</v>
+        <v>0.3209115726201317</v>
       </c>
     </row>
     <row r="18">
@@ -1138,31 +1138,31 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.5760283859890361</v>
+        <v>0.5518300341758322</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.4896927445480223</v>
+        <v>0.4813556038517585</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.4641609216140092</v>
+        <v>0.4680858711282094</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.4875489171772106</v>
+        <v>0.4818713526649803</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.3804068958485285</v>
+        <v>0.3720579677346967</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.3304118024216539</v>
+        <v>0.339650530879622</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.5196611328841555</v>
+        <v>0.5082161603494973</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.4287020752950155</v>
+        <v>0.4196961487405965</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.3913647415747844</v>
+        <v>0.3914969242414433</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1213,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 71,23%)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1313,28 +1313,28 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>6</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>16</v>
@@ -1348,28 +1348,28 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>14224</v>
+        <v>15111</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>13879</v>
+        <v>15631</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>4305</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>18051</v>
+        <v>23385</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>13169</v>
+        <v>15209</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>3772</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>32275</v>
+        <v>38497</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>27047</v>
+        <v>30840</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>8077</v>
@@ -1383,28 +1383,28 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>9973</v>
+        <v>10091</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>9833</v>
+        <v>11466</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>2424</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>13449</v>
+        <v>18444</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>9084</v>
+        <v>11272</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>1537</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>25827</v>
+        <v>31689</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>20901</v>
+        <v>24321</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>4986</v>
@@ -1418,28 +1418,28 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>18071</v>
+        <v>19497</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>17690</v>
+        <v>20331</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>6098</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>21971</v>
+        <v>28441</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>17912</v>
+        <v>19631</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>6870</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>38011</v>
+        <v>45781</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>32478</v>
+        <v>37236</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>11476</v>
@@ -1457,31 +1457,31 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>320</v>
+        <v>378</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>248</v>
+        <v>302</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9">
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>131195</v>
+        <v>153467</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>98871</v>
+        <v>120300</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>34801</v>
+        <v>35714</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>96295</v>
+        <v>115817</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>64246</v>
+        <v>77975</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>20654</v>
+        <v>22649</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>227490</v>
+        <v>269284</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>163117</v>
+        <v>198276</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>55455</v>
+        <v>58363</v>
       </c>
     </row>
     <row r="10">
@@ -1527,31 +1527,31 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>118236</v>
+        <v>139546</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>87000</v>
+        <v>107714</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>28546</v>
+        <v>29333</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>85169</v>
+        <v>103184</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>54593</v>
+        <v>67258</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>15707</v>
+        <v>17722</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>210410</v>
+        <v>251938</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>148256</v>
+        <v>182970</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>47078</v>
+        <v>49635</v>
       </c>
     </row>
     <row r="11">
@@ -1562,31 +1562,31 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>142422</v>
+        <v>166504</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>109837</v>
+        <v>134257</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>42049</v>
+        <v>42763</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>107326</v>
+        <v>127650</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>73844</v>
+        <v>88388</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>26580</v>
+        <v>27988</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>244054</v>
+        <v>287852</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>178642</v>
+        <v>217568</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>63832</v>
+        <v>67666</v>
       </c>
     </row>
     <row r="12">
@@ -1601,31 +1601,31 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>71608</v>
+        <v>85851</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>78130</v>
+        <v>90823</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>41987</v>
+        <v>44618</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>70781</v>
+        <v>79676</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>57635</v>
+        <v>66733</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>26386</v>
+        <v>29792</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>142389</v>
+        <v>165526</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>135765</v>
+        <v>157557</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>68373</v>
+        <v>74409</v>
       </c>
     </row>
     <row r="14">
@@ -1671,31 +1671,31 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>61641</v>
+        <v>76082</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>67602</v>
+        <v>79666</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>33389</v>
+        <v>35655</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>60720</v>
+        <v>69504</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>48056</v>
+        <v>56665</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>19761</v>
+        <v>22710</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>129514</v>
+        <v>151525</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>121404</v>
+        <v>142062</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>56957</v>
+        <v>61944</v>
       </c>
     </row>
     <row r="15">
@@ -1706,31 +1706,31 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>80312</v>
+        <v>95690</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>89148</v>
+        <v>101455</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>51833</v>
+        <v>54027</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>80224</v>
+        <v>89980</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>67928</v>
+        <v>77682</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>32900</v>
+        <v>37232</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>156454</v>
+        <v>180461</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>150209</v>
+        <v>172429</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>79889</v>
+        <v>86426</v>
       </c>
     </row>
     <row r="16">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>21</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
@@ -1780,31 +1780,31 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>63889</v>
+        <v>70651</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>46920</v>
+        <v>57306</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>40245</v>
+        <v>42647</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>40387</v>
+        <v>48273</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>34437</v>
+        <v>37010</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>15268</v>
+        <v>15269</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>104276</v>
+        <v>118924</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>81357</v>
+        <v>94317</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>55513</v>
+        <v>57915</v>
       </c>
     </row>
     <row r="18">
@@ -1815,31 +1815,31 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>54787</v>
+        <v>60315</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>37403</v>
+        <v>47053</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>30288</v>
+        <v>32357</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>31483</v>
+        <v>39259</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>26738</v>
+        <v>28156</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>9760</v>
+        <v>10013</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>90485</v>
+        <v>104775</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>69738</v>
+        <v>79842</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>43361</v>
+        <v>45922</v>
       </c>
     </row>
     <row r="19">
@@ -1850,31 +1850,31 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>75368</v>
+        <v>81026</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>57043</v>
+        <v>68435</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>51863</v>
+        <v>54656</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>49982</v>
+        <v>58412</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>42635</v>
+        <v>46244</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>22623</v>
+        <v>22945</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>117460</v>
+        <v>134597</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>93924</v>
+        <v>109128</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>68864</v>
+        <v>72633</v>
       </c>
     </row>
     <row r="20">
@@ -1889,31 +1889,31 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>725</v>
+        <v>843</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>590</v>
+        <v>699</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>272</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21">
@@ -1924,31 +1924,31 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>280916</v>
+        <v>325079</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>237801</v>
+        <v>284061</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>121338</v>
+        <v>127284</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>225514</v>
+        <v>267151</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>169486</v>
+        <v>196928</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>66080</v>
+        <v>71481</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>506430</v>
+        <v>592231</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>407287</v>
+        <v>480989</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>187419</v>
+        <v>198765</v>
       </c>
     </row>
     <row r="22">
@@ -1959,31 +1959,31 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>262560</v>
+        <v>303500</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>219700</v>
+        <v>262329</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>106201</v>
+        <v>111836</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>207320</v>
+        <v>246596</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>152738</v>
+        <v>178772</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>54849</v>
+        <v>60288</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>481200</v>
+        <v>564377</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>380987</v>
+        <v>452108</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>167434</v>
+        <v>179250</v>
       </c>
     </row>
     <row r="23">
@@ -1994,31 +1994,31 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>301398</v>
+        <v>345372</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>256707</v>
+        <v>303976</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>137074</v>
+        <v>145071</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>244101</v>
+        <v>287286</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>185334</v>
+        <v>214860</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>78050</v>
+        <v>84451</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>532083</v>
+        <v>621068</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>433598</v>
+        <v>507410</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>208024</v>
+        <v>218676</v>
       </c>
     </row>
     <row r="24">
